--- a/Jonail Jail/Enrolement of GBPS Jonail Jail.xlsx
+++ b/Jonail Jail/Enrolement of GBPS Jonail Jail.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\School\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Jonail Jail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F747A6F-52DF-40A0-ACB0-8FBB0D00A5BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E5E5FFF-53EB-4A05-BF95-80B06CAB71DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -171,9 +171,6 @@
     <t>5</t>
   </si>
   <si>
-    <t>Azlan Hussain</t>
-  </si>
-  <si>
     <t>Muhammad Rizwan</t>
   </si>
   <si>
@@ -1330,6 +1327,9 @@
   </si>
   <si>
     <t>GF.CNIC</t>
+  </si>
+  <si>
+    <t>Azaan Hussain</t>
   </si>
 </sst>
 </file>
@@ -1471,7 +1471,7 @@
     <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1762,26 +1762,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q139"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
@@ -1834,7 +1834,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1854,16 +1854,16 @@
         <v>408170018</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>48</v>
+        <v>434</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J2" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K2" s="15">
         <v>43750</v>
@@ -1872,13 +1872,13 @@
         <v>43508</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="P2" s="1" t="s">
         <v>36</v>
@@ -1887,7 +1887,7 @@
         <v>43508</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1907,16 +1907,16 @@
         <v>408170018</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K3" s="14">
         <v>41275</v>
@@ -1925,13 +1925,13 @@
         <v>44629</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="N3" s="18" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="P3" s="1" t="s">
         <v>36</v>
@@ -1940,7 +1940,7 @@
         <v>44629</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1960,40 +1960,40 @@
         <v>408170018</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K4" s="15">
         <v>43466</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N4" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="P4" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q4" s="15" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -2013,31 +2013,31 @@
         <v>408170018</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="L5" s="14">
         <v>45115</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N5" s="18" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="P5" s="1" t="s">
         <v>36</v>
@@ -2046,7 +2046,7 @@
         <v>45115</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -2066,31 +2066,31 @@
         <v>408170018</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K6" s="15" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L6" s="15">
         <v>44659</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N6" s="19" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="P6" s="1" t="s">
         <v>36</v>
@@ -2099,7 +2099,7 @@
         <v>44659</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -2119,16 +2119,16 @@
         <v>408170018</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>27</v>
       </c>
       <c r="J7" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K7" s="14">
         <v>42770</v>
@@ -2137,13 +2137,13 @@
         <v>45177</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="N7" s="18" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O7" s="5" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>36</v>
@@ -2152,7 +2152,7 @@
         <v>45177</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -2172,16 +2172,16 @@
         <v>408170018</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H8" s="9" t="s">
         <v>33</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K8" s="15">
         <v>43504</v>
@@ -2190,13 +2190,13 @@
         <v>45054</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N8" s="19" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>36</v>
@@ -2205,7 +2205,7 @@
         <v>45054</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -2225,31 +2225,31 @@
         <v>408170018</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="L9" s="14">
         <v>45146</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N9" s="18" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O9" s="5" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="P9" s="1" t="s">
         <v>36</v>
@@ -2258,7 +2258,7 @@
         <v>45146</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -2278,38 +2278,38 @@
         <v>408170018</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K10" s="15">
         <v>43221</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N10" s="19" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O10" s="4"/>
       <c r="P10" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -2329,38 +2329,38 @@
         <v>408170018</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H11" s="8" t="s">
         <v>18</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K11" s="14">
         <v>43101</v>
       </c>
       <c r="L11" s="14" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N11" s="18" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="O11" s="5"/>
       <c r="P11" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q11" s="14" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -2380,40 +2380,40 @@
         <v>408170018</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I12" s="9" t="s">
         <v>30</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N12" s="19" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P12" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -2433,40 +2433,40 @@
         <v>408170018</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K13" s="14">
         <v>43017</v>
       </c>
       <c r="L13" s="14" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N13" s="18" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O13" s="5" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="P13" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q13" s="14" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -2486,25 +2486,25 @@
         <v>408170018</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K14" s="15">
         <v>42370</v>
       </c>
       <c r="L14" s="15" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N14" s="19"/>
       <c r="O14" s="4"/>
@@ -2512,10 +2512,10 @@
         <v>36</v>
       </c>
       <c r="Q14" s="15" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -2535,40 +2535,40 @@
         <v>408170018</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K15" s="14">
         <v>41802</v>
       </c>
       <c r="L15" s="14" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N15" s="18" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O15" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="P15" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q15" s="14" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -2588,16 +2588,16 @@
         <v>408170018</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K16" s="15">
         <v>43961</v>
@@ -2606,13 +2606,13 @@
         <v>45177</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N16" s="19" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O16" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="P16" s="1" t="s">
         <v>36</v>
@@ -2621,7 +2621,7 @@
         <v>45177</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -2641,40 +2641,40 @@
         <v>408170018</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H17" s="8" t="s">
         <v>34</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K17" s="14" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="L17" s="14" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N17" s="18" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O17" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="P17" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q17" s="14" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -2694,16 +2694,16 @@
         <v>408170018</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K18" s="15">
         <v>43647</v>
@@ -2712,13 +2712,13 @@
         <v>45242</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N18" s="19" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="P18" s="1" t="s">
         <v>36</v>
@@ -2727,7 +2727,7 @@
         <v>45242</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -2747,25 +2747,25 @@
         <v>408170018</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I19" s="8" t="s">
         <v>32</v>
       </c>
       <c r="J19" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K19" s="14" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L19" s="14">
         <v>45177</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N19" s="18"/>
       <c r="O19" s="5"/>
@@ -2776,7 +2776,7 @@
         <v>45177</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -2796,31 +2796,31 @@
         <v>408170018</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="L20" s="15">
         <v>45119</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N20" s="19" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="P20" s="1" t="s">
         <v>36</v>
@@ -2829,7 +2829,7 @@
         <v>45119</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -2849,31 +2849,31 @@
         <v>408170018</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J21" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K21" s="14" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L21" s="14">
         <v>45119</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N21" s="18" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O21" s="5" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="P21" s="1" t="s">
         <v>36</v>
@@ -2882,7 +2882,7 @@
         <v>45119</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -2902,31 +2902,31 @@
         <v>408170018</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K22" s="15" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L22" s="15">
         <v>45352</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N22" s="19" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="O22" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="P22" s="1" t="s">
         <v>36</v>
@@ -2935,7 +2935,7 @@
         <v>45352</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -2955,16 +2955,16 @@
         <v>408170018</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J23" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K23" s="14">
         <v>43320</v>
@@ -2973,13 +2973,13 @@
         <v>45352</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N23" s="18" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="O23" s="5" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="P23" s="1" t="s">
         <v>36</v>
@@ -2988,7 +2988,7 @@
         <v>45352</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -3008,31 +3008,31 @@
         <v>408170018</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K24" s="15" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L24" s="15">
         <v>45352</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N24" s="19" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="O24" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="P24" s="1" t="s">
         <v>36</v>
@@ -3041,7 +3041,7 @@
         <v>45352</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -3061,16 +3061,16 @@
         <v>408170018</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J25" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K25" s="14">
         <v>42374</v>
@@ -3079,13 +3079,13 @@
         <v>45352</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N25" s="18" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="O25" s="5" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="P25" s="1" t="s">
         <v>36</v>
@@ -3094,7 +3094,7 @@
         <v>45352</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -3114,31 +3114,31 @@
         <v>408170018</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K26" s="15" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L26" s="15">
         <v>45566</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="N26" s="19" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="O26" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="P26" s="1" t="s">
         <v>36</v>
@@ -3147,7 +3147,7 @@
         <v>45566</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -3167,16 +3167,16 @@
         <v>408170018</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J27" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K27" s="14">
         <v>43138</v>
@@ -3185,13 +3185,13 @@
         <v>45566</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="N27" s="18" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="O27" s="5" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="P27" s="1" t="s">
         <v>36</v>
@@ -3200,7 +3200,7 @@
         <v>45566</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -3220,16 +3220,16 @@
         <v>408170018</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I28" s="9" t="s">
         <v>20</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K28" s="15">
         <v>40909</v>
@@ -3238,13 +3238,13 @@
         <v>45119</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N28" s="19" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O28" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="P28" s="1" t="s">
         <v>36</v>
@@ -3253,7 +3253,7 @@
         <v>45119</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -3273,40 +3273,40 @@
         <v>408170018</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J29" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K29" s="14">
         <v>42680</v>
       </c>
       <c r="L29" s="14" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N29" s="18" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="O29" s="5" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="P29" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q29" s="14" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -3326,38 +3326,38 @@
         <v>408170018</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K30" s="15">
         <v>43466</v>
       </c>
       <c r="L30" s="15" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N30" s="19" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="O30" s="4"/>
       <c r="P30" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q30" s="15" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -3377,16 +3377,16 @@
         <v>408170018</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J31" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K31" s="14">
         <v>43141</v>
@@ -3395,13 +3395,13 @@
         <v>45056</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N31" s="18" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O31" s="5" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="P31" s="1" t="s">
         <v>36</v>
@@ -3410,7 +3410,7 @@
         <v>45056</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -3430,16 +3430,16 @@
         <v>408170018</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K32" s="15">
         <v>42370</v>
@@ -3448,13 +3448,13 @@
         <v>45056</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N32" s="19" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="O32" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="P32" s="1" t="s">
         <v>36</v>
@@ -3463,7 +3463,7 @@
         <v>45056</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -3483,31 +3483,31 @@
         <v>408170018</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J33" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K33" s="14" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L33" s="14">
         <v>45056</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N33" s="18" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="O33" s="5" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P33" s="1" t="s">
         <v>36</v>
@@ -3516,7 +3516,7 @@
         <v>45056</v>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -3536,31 +3536,31 @@
         <v>408170018</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J34" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K34" s="15" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L34" s="15">
         <v>45056</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N34" s="19" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="O34" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P34" s="1" t="s">
         <v>36</v>
@@ -3569,7 +3569,7 @@
         <v>45056</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -3589,16 +3589,16 @@
         <v>408170018</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J35" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K35" s="14">
         <v>43466</v>
@@ -3607,13 +3607,13 @@
         <v>45056</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N35" s="18" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="O35" s="5" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="P35" s="1" t="s">
         <v>36</v>
@@ -3622,7 +3622,7 @@
         <v>45056</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -3642,16 +3642,16 @@
         <v>408170018</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K36" s="15">
         <v>42005</v>
@@ -3660,13 +3660,13 @@
         <v>45056</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N36" s="19" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="O36" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="P36" s="1" t="s">
         <v>36</v>
@@ -3675,7 +3675,7 @@
         <v>45056</v>
       </c>
     </row>
-    <row r="37" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -3695,16 +3695,16 @@
         <v>408170018</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J37" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K37" s="14">
         <v>42736</v>
@@ -3713,13 +3713,13 @@
         <v>45056</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N37" s="18" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="O37" s="5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="P37" s="1" t="s">
         <v>36</v>
@@ -3728,7 +3728,7 @@
         <v>45056</v>
       </c>
     </row>
-    <row r="38" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -3748,16 +3748,16 @@
         <v>408170018</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J38" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K38" s="15">
         <v>43831</v>
@@ -3766,13 +3766,13 @@
         <v>45056</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N38" s="19" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="O38" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="P38" s="1" t="s">
         <v>36</v>
@@ -3781,7 +3781,7 @@
         <v>45056</v>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -3801,40 +3801,40 @@
         <v>408170018</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J39" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K39" s="14" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L39" s="14" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N39" s="18" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="O39" s="5" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P39" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q39" s="14" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -3854,40 +3854,40 @@
         <v>408170018</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J40" s="12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K40" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="L40" s="15" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N40" s="19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O40" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="P40" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q40" s="15" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -3907,16 +3907,16 @@
         <v>408170018</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J41" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K41" s="14">
         <v>43112</v>
@@ -3925,13 +3925,13 @@
         <v>45056</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N41" s="18" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O41" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="P41" s="1" t="s">
         <v>36</v>
@@ -3940,7 +3940,7 @@
         <v>45056</v>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -3960,40 +3960,40 @@
         <v>408170018</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J42" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K42" s="15">
         <v>43101</v>
       </c>
       <c r="L42" s="15" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N42" s="19" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="O42" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="P42" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q42" s="15" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -4013,40 +4013,40 @@
         <v>408170018</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H43" s="11" t="s">
         <v>28</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J43" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K43" s="14">
         <v>43011</v>
       </c>
       <c r="L43" s="14" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N43" s="18" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="O43" s="5" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q43" s="14" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -4066,40 +4066,40 @@
         <v>408170018</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J44" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K44" s="15">
         <v>42430</v>
       </c>
       <c r="L44" s="15" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N44" s="19" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O44" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="P44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q44" s="15" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -4119,29 +4119,29 @@
         <v>408170018</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J45" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K45" s="14" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="L45" s="14">
         <v>44965</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N45" s="18"/>
       <c r="O45" s="5" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="P45" s="1" t="s">
         <v>36</v>
@@ -4150,7 +4150,7 @@
         <v>44965</v>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -4170,40 +4170,40 @@
         <v>408170018</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J46" s="12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K46" s="15">
         <v>42644</v>
       </c>
       <c r="L46" s="15" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="M46" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N46" s="19" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O46" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="P46" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q46" s="15" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -4223,40 +4223,40 @@
         <v>408170018</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J47" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K47" s="14">
         <v>42557</v>
       </c>
       <c r="L47" s="14" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="M47" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N47" s="18" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="O47" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="P47" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q47" s="14" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -4276,40 +4276,40 @@
         <v>408170018</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J48" s="12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K48" s="15">
         <v>42370</v>
       </c>
       <c r="L48" s="15" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="M48" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="N48" s="19" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="O48" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="P48" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q48" s="15" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -4329,40 +4329,40 @@
         <v>408170018</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J49" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K49" s="14">
         <v>42736</v>
       </c>
       <c r="L49" s="14" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="M49" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="N49" s="18" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="O49" s="5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="P49" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q49" s="14" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="50" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -4382,40 +4382,40 @@
         <v>408170018</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J50" s="12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K50" s="15">
         <v>43504</v>
       </c>
       <c r="L50" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="M50" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="N50" s="19" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="O50" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="P50" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q50" s="15" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -4435,40 +4435,40 @@
         <v>408170018</v>
       </c>
       <c r="G51" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="H51" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="I51" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="J51" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="K51" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="L51" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="M51" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="H51" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="I51" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="J51" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="K51" s="14" t="s">
-        <v>250</v>
-      </c>
-      <c r="L51" s="14" t="s">
-        <v>290</v>
-      </c>
-      <c r="M51" s="1" t="s">
-        <v>306</v>
-      </c>
       <c r="N51" s="18" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="O51" s="5" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="P51" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q51" s="14" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="52" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -4488,38 +4488,38 @@
         <v>408170018</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I52" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J52" s="12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K52" s="15">
         <v>2017</v>
       </c>
       <c r="L52" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N52" s="19" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="O52" s="4"/>
       <c r="P52" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q52" s="15" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -4539,40 +4539,40 @@
         <v>408170018</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H53" s="8" t="s">
         <v>16</v>
       </c>
       <c r="I53" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J53" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K53" s="14" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L53" s="14" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="M53" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N53" s="18" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O53" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="P53" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q53" s="14" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -4592,40 +4592,40 @@
         <v>408170018</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I54" s="9" t="s">
         <v>26</v>
       </c>
       <c r="J54" s="12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K54" s="15" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L54" s="15" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N54" s="19" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O54" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="P54" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="Q54" s="15" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -4645,40 +4645,40 @@
         <v>408170018</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I55" s="8" t="s">
         <v>26</v>
       </c>
       <c r="J55" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K55" s="14" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L55" s="14" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N55" s="18" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O55" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="P55" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="Q55" s="14" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -4698,38 +4698,38 @@
         <v>408170018</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I56" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J56" s="12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K56" s="15">
         <v>42370</v>
       </c>
       <c r="L56" s="15" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="M56" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N56" s="19" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="O56" s="4"/>
       <c r="P56" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q56" s="15" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -4749,16 +4749,16 @@
         <v>408170018</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J57" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K57" s="14">
         <v>43101</v>
@@ -4767,7 +4767,7 @@
         <v>44600</v>
       </c>
       <c r="M57" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N57" s="18"/>
       <c r="O57" s="5"/>
@@ -4778,7 +4778,7 @@
         <v>44600</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -4798,40 +4798,40 @@
         <v>408170018</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I58" s="9" t="s">
         <v>26</v>
       </c>
       <c r="J58" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K58" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="L58" s="15">
         <v>44601</v>
       </c>
       <c r="M58" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N58" s="19" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O58" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="Q58" s="15">
         <v>44601</v>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -4851,31 +4851,31 @@
         <v>408170018</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H59" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I59" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J59" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K59" s="14" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L59" s="14">
         <v>44601</v>
       </c>
       <c r="M59" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N59" s="18" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O59" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="P59" s="1" t="s">
         <v>36</v>
@@ -4884,7 +4884,7 @@
         <v>44601</v>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -4904,40 +4904,40 @@
         <v>408170018</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H60" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I60" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J60" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K60" s="15" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="L60" s="15">
         <v>44659</v>
       </c>
       <c r="M60" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N60" s="19" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="O60" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="P60" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="Q60" s="15">
         <v>44659</v>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -4957,16 +4957,16 @@
         <v>408170018</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J61" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K61" s="14">
         <v>42005</v>
@@ -4975,13 +4975,13 @@
         <v>44659</v>
       </c>
       <c r="M61" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="N61" s="18" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="O61" s="5" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="P61" s="1" t="s">
         <v>36</v>
@@ -4990,7 +4990,7 @@
         <v>44659</v>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -5010,16 +5010,16 @@
         <v>408170018</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H62" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I62" s="9" t="s">
         <v>31</v>
       </c>
       <c r="J62" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K62" s="15">
         <v>40179</v>
@@ -5028,11 +5028,11 @@
         <v>44014</v>
       </c>
       <c r="M62" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N62" s="19"/>
       <c r="O62" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="P62" s="1" t="s">
         <v>36</v>
@@ -5041,7 +5041,7 @@
         <v>44014</v>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -5061,16 +5061,16 @@
         <v>408170018</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H63" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I63" s="8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J63" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K63" s="14">
         <v>42705</v>
@@ -5079,13 +5079,13 @@
         <v>44629</v>
       </c>
       <c r="M63" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N63" s="18" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="O63" s="5" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="P63" s="1" t="s">
         <v>36</v>
@@ -5094,7 +5094,7 @@
         <v>44629</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -5114,40 +5114,40 @@
         <v>408170018</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H64" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I64" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J64" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K64" s="15" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="L64" s="15" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="M64" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N64" s="19" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="O64" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="P64" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q64" s="15" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="65" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -5167,16 +5167,16 @@
         <v>408170018</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I65" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J65" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K65" s="14">
         <v>41981</v>
@@ -5185,13 +5185,13 @@
         <v>45177</v>
       </c>
       <c r="M65" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N65" s="18" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="O65" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="P65" s="1" t="s">
         <v>36</v>
@@ -5200,7 +5200,7 @@
         <v>45177</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -5220,16 +5220,16 @@
         <v>408170018</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H66" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I66" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="J66" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K66" s="15">
         <v>40909</v>
@@ -5238,11 +5238,11 @@
         <v>44013</v>
       </c>
       <c r="M66" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N66" s="19"/>
       <c r="O66" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="P66" s="1" t="s">
         <v>36</v>
@@ -5251,7 +5251,7 @@
         <v>44013</v>
       </c>
     </row>
-    <row r="67" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -5271,40 +5271,40 @@
         <v>408170018</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H67" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I67" s="8" t="s">
         <v>30</v>
       </c>
       <c r="J67" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K67" s="14">
         <v>42106</v>
       </c>
       <c r="L67" s="14" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="M67" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N67" s="18" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="O67" s="5" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P67" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q67" s="14" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="68" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>67</v>
       </c>
@@ -5324,40 +5324,40 @@
         <v>408170018</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H68" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I68" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J68" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K68" s="15" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L68" s="15" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="M68" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N68" s="19" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O68" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="P68" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q68" s="15" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="69" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>68</v>
       </c>
@@ -5377,40 +5377,40 @@
         <v>408170018</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H69" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I69" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J69" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K69" s="14">
         <v>41279</v>
       </c>
       <c r="L69" s="14" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="M69" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N69" s="18" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="O69" s="5" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="P69" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q69" s="14" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="70" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>69</v>
       </c>
@@ -5430,16 +5430,16 @@
         <v>408170018</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H70" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I70" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J70" s="12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K70" s="15">
         <v>42463</v>
@@ -5448,13 +5448,13 @@
         <v>45056</v>
       </c>
       <c r="M70" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N70" s="19" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="O70" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P70" s="1" t="s">
         <v>36</v>
@@ -5463,7 +5463,7 @@
         <v>45056</v>
       </c>
     </row>
-    <row r="71" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>70</v>
       </c>
@@ -5483,16 +5483,16 @@
         <v>408170018</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H71" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I71" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J71" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K71" s="14">
         <v>42097</v>
@@ -5501,13 +5501,13 @@
         <v>44629</v>
       </c>
       <c r="M71" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N71" s="18" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O71" s="5" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="P71" s="1" t="s">
         <v>36</v>
@@ -5516,7 +5516,7 @@
         <v>44629</v>
       </c>
     </row>
-    <row r="72" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>71</v>
       </c>
@@ -5536,40 +5536,40 @@
         <v>408170018</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H72" s="9" t="s">
         <v>34</v>
       </c>
       <c r="I72" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J72" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K72" s="15" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L72" s="15" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="M72" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N72" s="19" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="O72" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="P72" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q72" s="15" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="73" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>72</v>
       </c>
@@ -5589,31 +5589,31 @@
         <v>408170018</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H73" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I73" s="8" t="s">
         <v>19</v>
       </c>
       <c r="J73" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K73" s="14" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L73" s="14">
         <v>44600</v>
       </c>
       <c r="M73" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N73" s="18" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="O73" s="5" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="P73" s="1" t="s">
         <v>36</v>
@@ -5622,7 +5622,7 @@
         <v>44600</v>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>73</v>
       </c>
@@ -5642,31 +5642,31 @@
         <v>408170018</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H74" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I74" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J74" s="12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K74" s="15" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="L74" s="15">
         <v>44659</v>
       </c>
       <c r="M74" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="N74" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="O74" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="P74" s="1" t="s">
         <v>36</v>
@@ -5675,7 +5675,7 @@
         <v>44659</v>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>74</v>
       </c>
@@ -5695,40 +5695,40 @@
         <v>408170018</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H75" s="8" t="s">
         <v>21</v>
       </c>
       <c r="I75" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J75" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K75" s="14" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="L75" s="14" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="M75" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N75" s="18" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O75" s="5" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="P75" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q75" s="14" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="76" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>75</v>
       </c>
@@ -5748,28 +5748,28 @@
         <v>408170018</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H76" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I76" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J76" s="12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K76" s="15">
         <v>42102</v>
       </c>
       <c r="L76" s="15" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="M76" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N76" s="19" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O76" s="4">
         <v>3203051164</v>
@@ -5778,10 +5778,10 @@
         <v>36</v>
       </c>
       <c r="Q76" s="15" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="77" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>76</v>
       </c>
@@ -5801,40 +5801,40 @@
         <v>408170018</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H77" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I77" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J77" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K77" s="14" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L77" s="14" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="M77" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N77" s="18" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O77" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="P77" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q77" s="14" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="78" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>77</v>
       </c>
@@ -5854,16 +5854,16 @@
         <v>408170018</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H78" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I78" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J78" s="12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K78" s="14">
         <v>41640</v>
@@ -5872,13 +5872,13 @@
         <v>45056</v>
       </c>
       <c r="M78" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N78" s="19" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="O78" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="P78" s="1" t="s">
         <v>36</v>
@@ -5887,7 +5887,7 @@
         <v>45056</v>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>78</v>
       </c>
@@ -5907,16 +5907,16 @@
         <v>408170018</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H79" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I79" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J79" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K79" s="14">
         <v>41855</v>
@@ -5925,11 +5925,11 @@
         <v>45505</v>
       </c>
       <c r="M79" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N79" s="18"/>
       <c r="O79" s="5" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="P79" s="1" t="s">
         <v>36</v>
@@ -5938,7 +5938,7 @@
         <v>45505</v>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>79</v>
       </c>
@@ -5958,40 +5958,40 @@
         <v>408170018</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H80" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I80" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J80" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K80" s="15">
         <v>41548</v>
       </c>
       <c r="L80" s="15" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="M80" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N80" s="19" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="O80" s="4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="P80" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q80" s="15" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="81" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>80</v>
       </c>
@@ -6011,31 +6011,31 @@
         <v>408170018</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H81" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I81" s="8" t="s">
         <v>19</v>
       </c>
       <c r="J81" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K81" s="14" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L81" s="14">
         <v>44600</v>
       </c>
       <c r="M81" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N81" s="18" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="O81" s="5" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="P81" s="1" t="s">
         <v>36</v>
@@ -6044,7 +6044,7 @@
         <v>44600</v>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>81</v>
       </c>
@@ -6064,16 +6064,16 @@
         <v>408170018</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H82" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I82" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J82" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K82" s="15">
         <v>42350</v>
@@ -6082,13 +6082,13 @@
         <v>44015</v>
       </c>
       <c r="M82" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N82" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="O82" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="P82" s="1" t="s">
         <v>36</v>
@@ -6097,7 +6097,7 @@
         <v>44015</v>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>82</v>
       </c>
@@ -6117,16 +6117,16 @@
         <v>408170018</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H83" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I83" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J83" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K83" s="14">
         <v>42311</v>
@@ -6135,13 +6135,13 @@
         <v>44013</v>
       </c>
       <c r="M83" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N83" s="18" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="O83" s="5" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="P83" s="1" t="s">
         <v>36</v>
@@ -6150,7 +6150,7 @@
         <v>44013</v>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>83</v>
       </c>
@@ -6170,16 +6170,16 @@
         <v>408170018</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H84" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I84" s="9" t="s">
         <v>31</v>
       </c>
       <c r="J84" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K84" s="15">
         <v>39814</v>
@@ -6188,7 +6188,7 @@
         <v>43473</v>
       </c>
       <c r="M84" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N84" s="19"/>
       <c r="O84" s="4">
@@ -6201,7 +6201,7 @@
         <v>43473</v>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>84</v>
       </c>
@@ -6221,31 +6221,31 @@
         <v>408170018</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H85" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I85" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J85" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K85" s="14" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L85" s="14">
         <v>44013</v>
       </c>
       <c r="M85" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N85" s="18" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O85" s="5" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="P85" s="1" t="s">
         <v>36</v>
@@ -6254,7 +6254,7 @@
         <v>44013</v>
       </c>
     </row>
-    <row r="86" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>85</v>
       </c>
@@ -6274,40 +6274,40 @@
         <v>408170018</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H86" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I86" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J86" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K86" s="15">
         <v>40273</v>
       </c>
       <c r="L86" s="15" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="M86" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N86" s="19" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="O86" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="P86" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q86" s="15" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="87" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>86</v>
       </c>
@@ -6327,31 +6327,31 @@
         <v>408170018</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H87" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I87" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J87" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K87" s="14" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="L87" s="14">
         <v>45242</v>
       </c>
       <c r="M87" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N87" s="18" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O87" s="5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="P87" s="1" t="s">
         <v>36</v>
@@ -6360,7 +6360,7 @@
         <v>45242</v>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>87</v>
       </c>
@@ -6380,16 +6380,16 @@
         <v>408170018</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H88" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I88" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J88" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K88" s="15">
         <v>41556</v>
@@ -6398,13 +6398,13 @@
         <v>44629</v>
       </c>
       <c r="M88" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N88" s="19" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O88" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="P88" s="1" t="s">
         <v>36</v>
@@ -6413,7 +6413,7 @@
         <v>44629</v>
       </c>
     </row>
-    <row r="89" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>88</v>
       </c>
@@ -6433,25 +6433,25 @@
         <v>408170018</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H89" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I89" s="8" t="s">
         <v>23</v>
       </c>
       <c r="J89" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K89" s="14" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="L89" s="14" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="M89" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N89" s="18"/>
       <c r="O89" s="5"/>
@@ -6459,10 +6459,10 @@
         <v>36</v>
       </c>
       <c r="Q89" s="14" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="90" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>89</v>
       </c>
@@ -6482,25 +6482,25 @@
         <v>408170018</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H90" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I90" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J90" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K90" s="15">
         <v>40909</v>
       </c>
       <c r="L90" s="15" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="M90" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N90" s="19"/>
       <c r="O90" s="4"/>
@@ -6508,10 +6508,10 @@
         <v>36</v>
       </c>
       <c r="Q90" s="15" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="91" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>90</v>
       </c>
@@ -6531,25 +6531,25 @@
         <v>408170018</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H91" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I91" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J91" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K91" s="14">
         <v>40909</v>
       </c>
       <c r="L91" s="14" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="M91" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N91" s="18"/>
       <c r="O91" s="5"/>
@@ -6557,10 +6557,10 @@
         <v>36</v>
       </c>
       <c r="Q91" s="14" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="92" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>91</v>
       </c>
@@ -6580,40 +6580,40 @@
         <v>408170018</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H92" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I92" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J92" s="12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K92" s="15">
         <v>41368</v>
       </c>
       <c r="L92" s="15" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="M92" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N92" s="19" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="O92" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="P92" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q92" s="15" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="93" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>92</v>
       </c>
@@ -6633,31 +6633,31 @@
         <v>408170018</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H93" s="8" t="s">
         <v>22</v>
       </c>
       <c r="I93" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J93" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K93" s="14" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="L93" s="14">
         <v>44015</v>
       </c>
       <c r="M93" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="N93" s="18" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="O93" s="5" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="P93" s="1" t="s">
         <v>36</v>
@@ -6666,7 +6666,7 @@
         <v>44015</v>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>93</v>
       </c>
@@ -6686,40 +6686,40 @@
         <v>408170018</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H94" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I94" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J94" s="12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K94" s="15">
         <v>40909</v>
       </c>
       <c r="L94" s="15" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="M94" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N94" s="19" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="O94" s="4" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="P94" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q94" s="15" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="95" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>94</v>
       </c>
@@ -6739,40 +6739,40 @@
         <v>408170018</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H95" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I95" s="8" t="s">
         <v>34</v>
       </c>
       <c r="J95" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K95" s="14">
         <v>42649</v>
       </c>
       <c r="L95" s="14" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="M95" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N95" s="18" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="O95" s="5" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="P95" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q95" s="14" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="96" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>95</v>
       </c>
@@ -6792,40 +6792,40 @@
         <v>408170018</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H96" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I96" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J96" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K96" s="15" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="L96" s="15" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="M96" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N96" s="19" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="O96" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="P96" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q96" s="15" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="97" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>96</v>
       </c>
@@ -6845,29 +6845,29 @@
         <v>408170018</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H97" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I97" s="8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J97" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K97" s="14" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L97" s="14">
         <v>44014</v>
       </c>
       <c r="M97" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N97" s="18"/>
       <c r="O97" s="5" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="P97" s="1" t="s">
         <v>36</v>
@@ -6876,7 +6876,7 @@
         <v>44014</v>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>97</v>
       </c>
@@ -6896,16 +6896,16 @@
         <v>408170018</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H98" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I98" s="9" t="s">
         <v>31</v>
       </c>
       <c r="J98" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K98" s="15">
         <v>40179</v>
@@ -6914,7 +6914,7 @@
         <v>44014</v>
       </c>
       <c r="M98" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N98" s="19"/>
       <c r="O98" s="5"/>
@@ -6925,7 +6925,7 @@
         <v>44014</v>
       </c>
     </row>
-    <row r="99" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>98</v>
       </c>
@@ -6945,16 +6945,16 @@
         <v>408170018</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H99" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I99" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J99" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K99" s="14">
         <v>40544</v>
@@ -6963,13 +6963,13 @@
         <v>44014</v>
       </c>
       <c r="M99" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N99" s="18" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="O99" s="5" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="P99" s="1" t="s">
         <v>36</v>
@@ -6978,7 +6978,7 @@
         <v>44014</v>
       </c>
     </row>
-    <row r="100" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>99</v>
       </c>
@@ -6998,16 +6998,16 @@
         <v>408170018</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H100" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I100" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J100" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K100" s="15">
         <v>40909</v>
@@ -7016,7 +7016,7 @@
         <v>44014</v>
       </c>
       <c r="M100" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N100" s="19"/>
       <c r="O100" s="4"/>
@@ -7027,7 +7027,7 @@
         <v>44014</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>100</v>
       </c>
@@ -7047,16 +7047,16 @@
         <v>408170018</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H101" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I101" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J101" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K101" s="14">
         <v>40909</v>
@@ -7065,7 +7065,7 @@
         <v>44014</v>
       </c>
       <c r="M101" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N101" s="18"/>
       <c r="O101" s="5"/>
@@ -7076,7 +7076,7 @@
         <v>44014</v>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>101</v>
       </c>
@@ -7096,16 +7096,16 @@
         <v>408170018</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H102" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I102" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J102" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K102" s="15">
         <v>40179</v>
@@ -7114,13 +7114,13 @@
         <v>44014</v>
       </c>
       <c r="M102" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N102" s="19" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="O102" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="P102" s="1" t="s">
         <v>36</v>
@@ -7129,7 +7129,7 @@
         <v>44014</v>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>102</v>
       </c>
@@ -7149,16 +7149,16 @@
         <v>408170018</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H103" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I103" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J103" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K103" s="14">
         <v>41275</v>
@@ -7167,13 +7167,13 @@
         <v>44014</v>
       </c>
       <c r="M103" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N103" s="18" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="O103" s="5" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="P103" s="1" t="s">
         <v>36</v>
@@ -7182,7 +7182,7 @@
         <v>44014</v>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>103</v>
       </c>
@@ -7202,31 +7202,31 @@
         <v>408170018</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H104" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I104" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J104" s="12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K104" s="15" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L104" s="15">
         <v>44014</v>
       </c>
       <c r="M104" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N104" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="O104" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="P104" s="1" t="s">
         <v>36</v>
@@ -7235,7 +7235,7 @@
         <v>44014</v>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>104</v>
       </c>
@@ -7255,16 +7255,16 @@
         <v>408170018</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H105" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I105" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J105" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K105" s="14">
         <v>40544</v>
@@ -7273,7 +7273,7 @@
         <v>44014</v>
       </c>
       <c r="M105" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N105" s="18"/>
       <c r="O105" s="5"/>
@@ -7284,7 +7284,7 @@
         <v>44014</v>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>105</v>
       </c>
@@ -7304,16 +7304,16 @@
         <v>408170018</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H106" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I106" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J106" s="12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K106" s="15">
         <v>39814</v>
@@ -7322,7 +7322,7 @@
         <v>44014</v>
       </c>
       <c r="M106" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N106" s="19"/>
       <c r="O106" s="4"/>
@@ -7333,7 +7333,7 @@
         <v>44014</v>
       </c>
     </row>
-    <row r="107" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>106</v>
       </c>
@@ -7353,16 +7353,16 @@
         <v>408170018</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H107" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I107" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J107" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K107" s="14">
         <v>40665</v>
@@ -7371,13 +7371,13 @@
         <v>45056</v>
       </c>
       <c r="M107" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N107" s="18" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="O107" s="5" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P107" s="1" t="s">
         <v>36</v>
@@ -7386,7 +7386,7 @@
         <v>45056</v>
       </c>
     </row>
-    <row r="108" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>107</v>
       </c>
@@ -7406,16 +7406,16 @@
         <v>408170018</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H108" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I108" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J108" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K108" s="15">
         <v>39448</v>
@@ -7424,13 +7424,13 @@
         <v>44015</v>
       </c>
       <c r="M108" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="N108" s="19" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="O108" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="P108" s="1" t="s">
         <v>36</v>
@@ -7439,7 +7439,7 @@
         <v>44015</v>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>108</v>
       </c>
@@ -7459,31 +7459,31 @@
         <v>408170018</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H109" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I109" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J109" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K109" s="14" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L109" s="14">
         <v>43985</v>
       </c>
       <c r="M109" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N109" s="18" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O109" s="5" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="P109" s="1" t="s">
         <v>36</v>
@@ -7492,7 +7492,7 @@
         <v>43985</v>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>109</v>
       </c>
@@ -7512,16 +7512,16 @@
         <v>408170018</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H110" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I110" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J110" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K110" s="16">
         <v>41338</v>
@@ -7530,13 +7530,13 @@
         <v>45242</v>
       </c>
       <c r="M110" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N110" s="20" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="P110" s="1" t="s">
         <v>36</v>
@@ -7545,7 +7545,7 @@
         <v>45242</v>
       </c>
     </row>
-    <row r="111" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B111" s="5">
         <v>789</v>
       </c>
@@ -7562,16 +7562,16 @@
         <v>408170018</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H111" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I111" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J111" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K111" s="14">
         <v>41640</v>
@@ -7580,22 +7580,22 @@
         <v>44014</v>
       </c>
       <c r="M111" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N111" s="18" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="O111" s="5" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="P111" s="17" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="Q111" s="14">
         <v>44014</v>
       </c>
     </row>
-    <row r="112" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B112" s="4">
         <v>797</v>
       </c>
@@ -7612,16 +7612,16 @@
         <v>408170018</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H112" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I112" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J112" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K112" s="15">
         <v>40910</v>
@@ -7630,13 +7630,13 @@
         <v>44629</v>
       </c>
       <c r="M112" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N112" s="19" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O112" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="P112" s="17" t="s">
         <v>36</v>
@@ -7645,7 +7645,7 @@
         <v>44629</v>
       </c>
     </row>
-    <row r="113" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B113" s="5">
         <v>786</v>
       </c>
@@ -7662,16 +7662,16 @@
         <v>408170018</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H113" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I113" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J113" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K113" s="14">
         <v>40736</v>
@@ -7680,13 +7680,13 @@
         <v>44013</v>
       </c>
       <c r="M113" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N113" s="18" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O113" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="P113" s="17" t="s">
         <v>36</v>
@@ -7695,7 +7695,7 @@
         <v>44013</v>
       </c>
     </row>
-    <row r="114" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B114" s="4">
         <v>787</v>
       </c>
@@ -7712,16 +7712,16 @@
         <v>408170018</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H114" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I114" s="9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J114" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K114" s="15">
         <v>41610</v>
@@ -7730,13 +7730,13 @@
         <v>44013</v>
       </c>
       <c r="M114" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N114" s="19" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O114" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="P114" s="17" t="s">
         <v>36</v>
@@ -7745,7 +7745,7 @@
         <v>44013</v>
       </c>
     </row>
-    <row r="115" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B115" s="5">
         <v>751</v>
       </c>
@@ -7762,25 +7762,25 @@
         <v>408170018</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H115" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I115" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J115" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K115" s="14" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="L115" s="14">
         <v>42833</v>
       </c>
       <c r="M115" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N115" s="18"/>
       <c r="O115" s="5"/>
@@ -7791,7 +7791,7 @@
         <v>42833</v>
       </c>
     </row>
-    <row r="116" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B116" s="4">
         <v>765</v>
       </c>
@@ -7808,31 +7808,31 @@
         <v>408170018</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H116" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I116" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J116" s="12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K116" s="15" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="L116" s="15">
         <v>43473</v>
       </c>
       <c r="M116" s="17" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="N116" s="19" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="O116" s="5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="P116" s="17" t="s">
         <v>36</v>
@@ -7841,7 +7841,7 @@
         <v>43473</v>
       </c>
     </row>
-    <row r="117" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B117" s="5">
         <v>768</v>
       </c>
@@ -7858,16 +7858,16 @@
         <v>408170018</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H117" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I117" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J117" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K117" s="14">
         <v>42097</v>
@@ -7876,13 +7876,13 @@
         <v>43473</v>
       </c>
       <c r="M117" s="17" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="N117" s="18" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="O117" s="5" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="P117" s="17" t="s">
         <v>36</v>
@@ -7891,7 +7891,7 @@
         <v>43473</v>
       </c>
     </row>
-    <row r="118" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B118" s="4">
         <v>776</v>
       </c>
@@ -7908,16 +7908,16 @@
         <v>408170018</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H118" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I118" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J118" s="12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K118" s="15">
         <v>42067</v>
@@ -7926,13 +7926,13 @@
         <v>44013</v>
       </c>
       <c r="M118" s="17" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N118" s="19" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="O118" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="P118" s="17" t="s">
         <v>36</v>
@@ -7941,7 +7941,7 @@
         <v>44013</v>
       </c>
     </row>
-    <row r="119" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B119" s="5">
         <v>793</v>
       </c>
@@ -7958,16 +7958,16 @@
         <v>408170018</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H119" s="8" t="s">
         <v>29</v>
       </c>
       <c r="I119" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J119" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K119" s="14">
         <v>42005</v>
@@ -7976,13 +7976,13 @@
         <v>44013</v>
       </c>
       <c r="M119" s="17" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="N119" s="18" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="O119" s="5" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="P119" s="17" t="s">
         <v>36</v>
@@ -7991,7 +7991,7 @@
         <v>44013</v>
       </c>
     </row>
-    <row r="120" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B120" s="6" t="s">
         <v>37</v>
       </c>
@@ -8008,40 +8008,40 @@
         <v>408170018</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H120" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I120" s="9" t="s">
         <v>27</v>
       </c>
       <c r="J120" s="12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K120" s="14">
         <v>40675</v>
       </c>
       <c r="L120" s="15" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="M120" s="17" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="N120" s="19" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O120" s="5" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="P120" s="17" t="s">
         <v>36</v>
       </c>
       <c r="Q120" s="15" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="121" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="121" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B121" s="7" t="s">
         <v>38</v>
       </c>
@@ -8058,16 +8058,16 @@
         <v>408170018</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H121" s="11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I121" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="J121" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K121" s="14">
         <v>40859</v>
@@ -8076,13 +8076,13 @@
         <v>42804</v>
       </c>
       <c r="M121" s="17" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N121" s="18" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="O121" s="5" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="P121" s="17" t="s">
         <v>36</v>
@@ -8091,7 +8091,7 @@
         <v>42804</v>
       </c>
     </row>
-    <row r="122" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B122" s="6" t="s">
         <v>39</v>
       </c>
@@ -8108,16 +8108,16 @@
         <v>408170018</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H122" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I122" s="9" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J122" s="12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K122" s="15">
         <v>40179</v>
@@ -8126,7 +8126,7 @@
         <v>45242</v>
       </c>
       <c r="M122" s="17" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N122" s="19"/>
       <c r="O122" s="4"/>
@@ -8137,7 +8137,7 @@
         <v>45242</v>
       </c>
     </row>
-    <row r="123" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B123" s="7" t="s">
         <v>40</v>
       </c>
@@ -8154,31 +8154,31 @@
         <v>408170018</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H123" s="11" t="s">
         <v>21</v>
       </c>
       <c r="I123" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J123" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K123" s="14" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L123" s="14">
         <v>43383</v>
       </c>
       <c r="M123" s="17" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N123" s="18" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O123" s="5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="P123" s="17" t="s">
         <v>36</v>
@@ -8187,7 +8187,7 @@
         <v>43383</v>
       </c>
     </row>
-    <row r="124" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="124" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B124" s="6" t="s">
         <v>41</v>
       </c>
@@ -8204,16 +8204,16 @@
         <v>408170018</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H124" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I124" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J124" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K124" s="15">
         <v>39934</v>
@@ -8222,13 +8222,13 @@
         <v>42833</v>
       </c>
       <c r="M124" s="17" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="N124" s="19" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="O124" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="P124" s="17" t="s">
         <v>36</v>
@@ -8237,7 +8237,7 @@
         <v>42833</v>
       </c>
     </row>
-    <row r="125" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="125" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B125" s="5">
         <v>770</v>
       </c>
@@ -8254,16 +8254,16 @@
         <v>408170018</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H125" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I125" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J125" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K125" s="14">
         <v>41276</v>
@@ -8272,13 +8272,13 @@
         <v>42833</v>
       </c>
       <c r="M125" s="17" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N125" s="18" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="O125" s="5" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="P125" s="17" t="s">
         <v>36</v>
@@ -8287,7 +8287,7 @@
         <v>42833</v>
       </c>
     </row>
-    <row r="126" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B126" s="4">
         <v>771</v>
       </c>
@@ -8304,16 +8304,16 @@
         <v>408170018</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H126" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I126" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J126" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K126" s="15">
         <v>40909</v>
@@ -8322,22 +8322,22 @@
         <v>42833</v>
       </c>
       <c r="M126" s="17" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N126" s="19" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="O126" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="P126" s="17" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="Q126" s="15">
         <v>42833</v>
       </c>
     </row>
-    <row r="127" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="127" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B127" s="5">
         <v>772</v>
       </c>
@@ -8354,31 +8354,31 @@
         <v>408170018</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H127" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I127" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J127" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K127" s="14" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L127" s="14">
         <v>43562</v>
       </c>
       <c r="M127" s="17" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N127" s="18" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="O127" s="5" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="P127" s="17" t="s">
         <v>36</v>
@@ -8387,7 +8387,7 @@
         <v>43562</v>
       </c>
     </row>
-    <row r="128" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="128" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B128" s="4">
         <v>773</v>
       </c>
@@ -8404,16 +8404,16 @@
         <v>408170018</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H128" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I128" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J128" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K128" s="15">
         <v>41551</v>
@@ -8422,13 +8422,13 @@
         <v>43562</v>
       </c>
       <c r="M128" s="17" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N128" s="19" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="O128" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="P128" s="17" t="s">
         <v>36</v>
@@ -8437,7 +8437,7 @@
         <v>43562</v>
       </c>
     </row>
-    <row r="129" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="129" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B129" s="5">
         <v>775</v>
       </c>
@@ -8454,31 +8454,31 @@
         <v>408170018</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H129" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I129" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J129" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K129" s="14" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L129" s="14">
         <v>43562</v>
       </c>
       <c r="M129" s="17" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N129" s="18" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O129" s="5" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="P129" s="17" t="s">
         <v>36</v>
@@ -8487,7 +8487,7 @@
         <v>43562</v>
       </c>
     </row>
-    <row r="130" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B130" s="4">
         <v>792</v>
       </c>
@@ -8504,31 +8504,31 @@
         <v>408170018</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H130" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I130" s="9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J130" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K130" s="15" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="L130" s="15">
         <v>44013</v>
       </c>
       <c r="M130" s="17" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N130" s="19" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="O130" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="P130" s="17" t="s">
         <v>36</v>
@@ -8537,7 +8537,7 @@
         <v>44013</v>
       </c>
     </row>
-    <row r="131" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B131" s="5">
         <v>796</v>
       </c>
@@ -8554,16 +8554,16 @@
         <v>408170018</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H131" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I131" s="8" t="s">
         <v>19</v>
       </c>
       <c r="J131" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K131" s="14">
         <v>40179</v>
@@ -8572,13 +8572,13 @@
         <v>44600</v>
       </c>
       <c r="M131" s="17" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N131" s="18" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="O131" s="5" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="P131" s="17" t="s">
         <v>36</v>
@@ -8587,7 +8587,7 @@
         <v>44600</v>
       </c>
     </row>
-    <row r="132" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="132" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B132" s="4">
         <v>748</v>
       </c>
@@ -8604,16 +8604,16 @@
         <v>408170018</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H132" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I132" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="J132" s="12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K132" s="15">
         <v>40088</v>
@@ -8622,7 +8622,7 @@
         <v>42864</v>
       </c>
       <c r="M132" s="17" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N132" s="19"/>
       <c r="O132" s="4"/>
@@ -8633,7 +8633,7 @@
         <v>42864</v>
       </c>
     </row>
-    <row r="133" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="133" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B133" s="5">
         <v>777</v>
       </c>
@@ -8650,16 +8650,16 @@
         <v>408170018</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H133" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I133" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J133" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K133" s="14">
         <v>41034</v>
@@ -8668,13 +8668,13 @@
         <v>43383</v>
       </c>
       <c r="M133" s="17" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="N133" s="18" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="O133" s="5" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="P133" s="17" t="s">
         <v>36</v>
@@ -8683,7 +8683,7 @@
         <v>43383</v>
       </c>
     </row>
-    <row r="134" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="134" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B134" s="4">
         <v>717</v>
       </c>
@@ -8700,16 +8700,16 @@
         <v>408170018</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H134" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I134" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J134" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K134" s="15">
         <v>40454</v>
@@ -8718,13 +8718,13 @@
         <v>43383</v>
       </c>
       <c r="M134" s="17" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="N134" s="19" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="O134" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="P134" s="17" t="s">
         <v>36</v>
@@ -8733,7 +8733,7 @@
         <v>43383</v>
       </c>
     </row>
-    <row r="135" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="135" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B135" s="5">
         <v>718</v>
       </c>
@@ -8750,31 +8750,31 @@
         <v>408170018</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H135" s="8" t="s">
         <v>17</v>
       </c>
       <c r="I135" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J135" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K135" s="14" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="L135" s="14">
         <v>42799</v>
       </c>
       <c r="M135" s="17" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N135" s="18" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O135" s="5" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="P135" s="17" t="s">
         <v>36</v>
@@ -8783,7 +8783,7 @@
         <v>42799</v>
       </c>
     </row>
-    <row r="136" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="136" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B136" s="4">
         <v>725</v>
       </c>
@@ -8800,31 +8800,31 @@
         <v>408170018</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H136" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I136" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J136" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K136" s="15" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="L136" s="15">
         <v>42377</v>
       </c>
       <c r="M136" s="17" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="N136" s="19" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="O136" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="P136" s="17" t="s">
         <v>36</v>
@@ -8833,7 +8833,7 @@
         <v>42377</v>
       </c>
     </row>
-    <row r="137" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="137" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B137" s="5">
         <v>736</v>
       </c>
@@ -8850,31 +8850,31 @@
         <v>408170018</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H137" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I137" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="J137" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="J137" s="13" t="s">
-        <v>232</v>
-      </c>
       <c r="K137" s="14" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L137" s="14">
         <v>42798</v>
       </c>
       <c r="M137" s="17" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N137" s="18" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O137" s="5" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="P137" s="17" t="s">
         <v>36</v>
@@ -8883,7 +8883,7 @@
         <v>42798</v>
       </c>
     </row>
-    <row r="138" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="138" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B138" s="4">
         <v>760</v>
       </c>
@@ -8900,16 +8900,16 @@
         <v>408170018</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H138" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I138" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J138" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K138" s="15">
         <v>40546</v>
@@ -8918,13 +8918,13 @@
         <v>43472</v>
       </c>
       <c r="M138" s="17" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N138" s="19" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="O138" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="P138" s="17" t="s">
         <v>36</v>
@@ -8933,7 +8933,7 @@
         <v>43472</v>
       </c>
     </row>
-    <row r="139" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="139" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B139" s="5">
         <v>769</v>
       </c>
@@ -8950,16 +8950,16 @@
         <v>408170018</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H139" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I139" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J139" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K139" s="14">
         <v>41761</v>
@@ -8968,13 +8968,13 @@
         <v>43383</v>
       </c>
       <c r="M139" s="17" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="N139" s="18" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="O139" s="5" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="P139" s="17" t="s">
         <v>36</v>
